--- a/erp-server/erp-server-file/src/main/resources/excel/oms/deliveryBoxRule.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/deliveryBoxRule.xlsx
@@ -40,7 +40,7 @@
     <t>发货SKU</t>
   </si>
   <si>
-    <t>发货箱规</t>
+    <t>单箱数量</t>
   </si>
   <si>
     <t>状态</t>
